--- a/invoices/invoice_2026-10-22.xlsx
+++ b/invoices/invoice_2026-10-22.xlsx
@@ -694,14 +694,14 @@
     <row r="16" ht="28" customHeight="1">
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Project Management</t>
+          <t>Professional Consulting Services</t>
         </is>
       </c>
       <c r="C16" s="12" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="D16" s="13" t="n">
-        <v>450000</v>
+        <v>500000</v>
       </c>
       <c r="E16" s="14" t="n">
         <v>0.11</v>
@@ -714,14 +714,14 @@
     <row r="17" ht="28" customHeight="1">
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>UI/UX Design Services</t>
+          <t>Project Management</t>
         </is>
       </c>
       <c r="C17" s="12" t="n">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="D17" s="13" t="n">
-        <v>750000</v>
+        <v>450000</v>
       </c>
       <c r="E17" s="14" t="n">
         <v>0.11</v>
